--- a/app/static/storage/JEPS BUSSINESS.xlsx
+++ b/app/static/storage/JEPS BUSSINESS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Supreme Court\Desktop\Clerk II\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF1A91D-0BCE-4F94-8495-6C71F0DDA828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4488746D-A47D-41AC-A4C5-448A9E11A482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3CE4B30-2660-46A7-95C6-9CC23917F654}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="98">
   <si>
     <t>No.</t>
   </si>
@@ -326,6 +326,12 @@
   </si>
   <si>
     <t>JEPS-2026-000311335</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000320423</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000324035</t>
   </si>
 </sst>
 </file>
@@ -3409,11 +3415,11 @@
       </c>
       <c r="O2" s="3">
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="P2" s="34">
         <f>SUM(O2:O4)</f>
-        <v>340</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -3499,7 +3505,7 @@
       </c>
       <c r="O4" s="9">
         <f>SUMIFS(E:E, H:H, "")</f>
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="P4" s="34"/>
     </row>
@@ -3580,14 +3586,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="C7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3">
+        <v>90</v>
+      </c>
+      <c r="E7" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="H7" s="15"/>
       <c r="J7" s="14">
         <v>46233</v>
@@ -3611,14 +3625,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="C8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="3">
+        <v>100</v>
+      </c>
+      <c r="E8" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="H8" s="15"/>
       <c r="J8" s="14">
         <v>46246</v>

--- a/app/static/storage/JEPS BUSSINESS.xlsx
+++ b/app/static/storage/JEPS BUSSINESS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyZar\app\static\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4488746D-A47D-41AC-A4C5-448A9E11A482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01621592-40D5-4A55-8C5C-1E4008EE08C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{E3CE4B30-2660-46A7-95C6-9CC23917F654}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="104">
   <si>
     <t>No.</t>
   </si>
@@ -332,6 +332,24 @@
   </si>
   <si>
     <t>JEPS-2026-000324035</t>
+  </si>
+  <si>
+    <t>STF</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000326360</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000329283</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000321185</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000336894</t>
+  </si>
+  <si>
+    <t>JEPS-2026-000336873</t>
   </si>
 </sst>
 </file>
@@ -3281,7 +3299,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13D4D6AF-B61D-464D-9E7F-C6E9749645A3}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33" bestFit="1" customWidth="1"/>
@@ -3310,6 +3328,11 @@
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3328,8 +3351,8 @@
     <col min="1" max="1" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="1" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="34.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" style="1" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.140625" style="1" customWidth="1"/>
@@ -3398,8 +3421,8 @@
       <c r="G2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="H2" s="15" t="s">
-        <v>32</v>
+      <c r="H2" s="15">
+        <v>1</v>
       </c>
       <c r="J2" s="11" t="s">
         <v>11</v>
@@ -3415,11 +3438,11 @@
       </c>
       <c r="O2" s="3">
         <f>SUMIFS(D:D, F:F, "CASH", H:H, "")</f>
-        <v>190</v>
+        <v>540</v>
       </c>
       <c r="P2" s="34">
         <f>SUM(O2:O4)</f>
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -3444,8 +3467,8 @@
       <c r="G3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H3" s="15" t="s">
-        <v>32</v>
+      <c r="H3" s="15">
+        <v>1</v>
       </c>
       <c r="J3" s="14">
         <v>46217</v>
@@ -3461,7 +3484,7 @@
       </c>
       <c r="O3" s="3">
         <f>SUMIFS(D:D, F:F, "GCASH", H:H, "")</f>
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="P3" s="34"/>
     </row>
@@ -3487,8 +3510,8 @@
       <c r="G4" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H4" s="15" t="s">
-        <v>32</v>
+      <c r="H4" s="15">
+        <v>1</v>
       </c>
       <c r="J4" s="14">
         <v>46219</v>
@@ -3505,7 +3528,7 @@
       </c>
       <c r="O4" s="9">
         <f>SUMIFS(E:E, H:H, "")</f>
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="P4" s="34"/>
     </row>
@@ -3531,8 +3554,8 @@
       <c r="G5" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="15" t="s">
-        <v>32</v>
+      <c r="H5" s="15">
+        <v>1</v>
       </c>
       <c r="J5" s="14">
         <v>46219</v>
@@ -3568,7 +3591,9 @@
       <c r="G6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H6" s="15"/>
+      <c r="H6" s="15">
+        <v>2</v>
+      </c>
       <c r="J6" s="14">
         <v>46226</v>
       </c>
@@ -3602,7 +3627,9 @@
       <c r="G7" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H7" s="15"/>
+      <c r="H7" s="15">
+        <v>2</v>
+      </c>
       <c r="J7" s="14">
         <v>46233</v>
       </c>
@@ -3641,7 +3668,9 @@
       <c r="G8" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H8" s="15"/>
+      <c r="H8" s="15">
+        <v>2</v>
+      </c>
       <c r="J8" s="14">
         <v>46246</v>
       </c>
@@ -3655,7 +3684,7 @@
         <v>92</v>
       </c>
       <c r="O8" s="1">
-        <v>1680</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -3664,15 +3693,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="15"/>
+      <c r="C9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="15">
+        <v>2</v>
+      </c>
       <c r="J9" s="17"/>
       <c r="K9" s="3"/>
       <c r="L9" s="15"/>
@@ -3681,7 +3720,7 @@
       </c>
       <c r="O9" s="1">
         <f>O8-O7</f>
-        <v>120</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -3690,15 +3729,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="15"/>
+      <c r="C10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="15">
+        <v>2</v>
+      </c>
       <c r="J10" s="17"/>
       <c r="K10" s="3"/>
       <c r="L10" s="15"/>
@@ -3709,15 +3758,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="15"/>
+      <c r="C11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="3">
+        <v>90</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="15">
+        <v>2</v>
+      </c>
       <c r="J11" s="17"/>
       <c r="K11" s="3"/>
       <c r="L11" s="15"/>
@@ -3728,14 +3787,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
+      <c r="C12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="3">
+        <v>240</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>102</v>
+      </c>
       <c r="H12" s="15"/>
       <c r="J12" s="17"/>
       <c r="K12" s="3"/>
@@ -3747,14 +3814,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="C13" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="3">
+        <v>300</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="H13" s="15"/>
       <c r="J13" s="17"/>
       <c r="K13" s="3"/>
@@ -6853,7 +6928,7 @@
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F045D2E2-0E72-44E8-9E97-B2F395439637}">
           <x14:formula1>
-            <xm:f>Sheet3!$A$1:$A$5</xm:f>
+            <xm:f>Sheet3!$A$1:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C201</xm:sqref>
         </x14:dataValidation>
